--- a/dados/excel/local_map.xlsx
+++ b/dados/excel/local_map.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Legenda — Tipos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda — Tipos" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$G$473</definedName>
@@ -713,7 +713,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10/10/2026 14:55</t>
+          <t>12/10/2026 16:30</t>
         </is>
       </c>
     </row>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="B3" s="30" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -16494,7 +16494,7 @@
       </c>
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -16518,7 +16518,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -16530,7 +16530,7 @@
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="B10" s="36" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>

--- a/dados/excel/local_map.xlsx
+++ b/dados/excel/local_map.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026 16:30</t>
+          <t>16/10/2026 19:58</t>
         </is>
       </c>
     </row>
